--- a/data/country_baselines/Updated/Baseline information_Zambia SS.xlsx
+++ b/data/country_baselines/Updated/Baseline information_Zambia SS.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/data/country_baselines/Updated/Baseline information_Zambia SS.xlsx
+++ b/data/country_baselines/Updated/Baseline information_Zambia SS.xlsx
@@ -417,10 +417,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
